--- a/data/trans_dic/KIDM_A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,86</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 10,99</t>
+          <t>1,21; 11,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,19</t>
+          <t>0,0; 10,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,1</t>
+          <t>1,01; 9,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 9,79</t>
+          <t>0,98; 9,38</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 11,97</t>
+          <t>1,09; 11,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,12</t>
+          <t>0,68; 6,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,01</t>
+          <t>1,73; 8,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,55; 6,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 4,1</t>
         </is>
       </c>
     </row>
@@ -861,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,4</t>
+          <t>0,75; 7,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 4,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,41</t>
+          <t>0,0; 7,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 6,73</t>
+          <t>0,74; 6,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,16; 10,15</t>
+          <t>2,04; 9,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,86</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,25</t>
+          <t>0,74; 6,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,57</t>
+          <t>1,03; 4,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,24</t>
+          <t>2,18; 6,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,01</t>
+          <t>0,34; 3,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,76</t>
+          <t>0,51; 4,86</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,78</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,69</t>
+          <t>0,0; 7,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,91</t>
+          <t>1,6; 10,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>0,0; 5,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 5,18</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,97</t>
+          <t>0,0; 3,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,92</t>
+          <t>0,5; 4,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,05</t>
+          <t>1,2; 6,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
     </row>
@@ -1136,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,71</t>
+          <t>0,9; 7,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,95; 8,24</t>
+          <t>0,96; 8,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,47 +1152,47 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,53</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,76</t>
+          <t>0,78; 7,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,13</t>
+          <t>0,43; 4,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,53</t>
+          <t>1,63; 6,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,4</t>
+          <t>0,15; 5,22</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,9</t>
+          <t>0,99; 4,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,21</t>
+          <t>1,68; 5,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,95</t>
+          <t>0,7; 2,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,17</t>
+          <t>0,32; 3,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,47</t>
+          <t>0,89; 3,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,77</t>
+          <t>2,16; 5,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,47</t>
+          <t>0,75; 3,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,0</t>
+          <t>0,37; 3,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 3,25</t>
+          <t>1,23; 3,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,84</t>
+          <t>2,28; 4,75</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,62</t>
+          <t>0,99; 2,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,4</t>
+          <t>0,56; 2,45</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2390</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2838</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3740</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5228</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5004</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>707; 6884</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3354</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>667; 6175</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>669; 6431</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>722; 7347</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>830; 7761</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2192; 10455</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>712; 7787</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3249</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1825</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1166</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2675</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4571</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2498</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7219</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2508</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3282</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>533; 4908</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>673; 6588</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4300</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3999</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>681; 6171</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1839; 8599</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5140</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>763; 7147</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1945; 9009</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>3935; 12151</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>667; 6214</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>796; 7608</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3132</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1190</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3831</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>416</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3482</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4733</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1045; 6627</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2668</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3335</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3568</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3516</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4526</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>644; 6031</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1597; 8352</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2622</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2971</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>753</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2784</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2187</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5754</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>680; 5862</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>787; 7397</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3732</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4518</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>679; 6793</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3367</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6228</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>682; 6415</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2771; 10632</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4926</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>165; 5732</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>6085</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>9344</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5051</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5634</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11382</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5546</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>11719</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>20726</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>10597</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>2795; 11970</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4907; 15396</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2254; 9348</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>684; 6553</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2687; 10342</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>6736; 17923</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2453; 11722</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1015; 8430</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>7173; 18806</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13781; 28689</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6434; 16695</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2712; 11845</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_A_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_A_R-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 8,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 11,81</t>
+          <t>1,21; 10,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,22 +732,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,76</t>
+          <t>0,0; 11,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 9,36</t>
+          <t>1,01; 8,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 9,38</t>
+          <t>1,0; 9,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 11,12</t>
+          <t>0,0; 11,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,38</t>
+          <t>1,18; 6,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,24</t>
+          <t>1,69; 7,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 6,02</t>
+          <t>0,55; 6,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,1</t>
+          <t>0,0; 4,86</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,08</t>
+          <t>0,55; 5,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 7,3</t>
+          <t>0,75; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,43</t>
+          <t>0,0; 4,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,46</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,75</t>
+          <t>0,75; 7,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,53</t>
+          <t>2,16; 9,64</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,24</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,95</t>
+          <t>0,75; 6,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,79</t>
+          <t>1,01; 4,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,73</t>
+          <t>2,18; 6,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,18</t>
+          <t>0,33; 3,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,86</t>
+          <t>0,54; 5,33</t>
         </is>
       </c>
     </row>
@@ -997,37 +997,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,71</t>
+          <t>0,0; 7,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,6; 10,15</t>
+          <t>1,76; 10,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,65</t>
+          <t>0,0; 4,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,39</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,18</t>
+          <t>0,0; 6,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1037,22 +1037,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,89</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,73</t>
+          <t>0,5; 4,53</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 6,27</t>
+          <t>0,97; 5,95</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,52</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,9; 7,79</t>
+          <t>0,9; 8,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,99</t>
+          <t>0,97; 9,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,45</t>
+          <t>0,0; 7,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 7,79</t>
+          <t>0,78; 7,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 8,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,03</t>
+          <t>0,43; 4,16</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,27</t>
+          <t>1,67; 6,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 5,22</t>
+          <t>0,15; 4,96</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,23</t>
+          <t>0,99; 3,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,27</t>
+          <t>1,87; 5,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,88</t>
+          <t>0,67; 2,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,1</t>
+          <t>0,35; 3,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,42</t>
+          <t>0,83; 3,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,74</t>
+          <t>2,28; 5,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,6</t>
+          <t>0,75; 3,45</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,09</t>
+          <t>0,38; 3,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,21</t>
+          <t>1,16; 3,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,75</t>
+          <t>2,22; 4,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,57</t>
+          <t>0,91; 2,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,45</t>
+          <t>0,55; 2,58</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor) (tasa de respuesta: 91,02%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala (tasa de respuesta: 91,02%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5004</t>
+          <t>0; 4781</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>707; 6884</t>
+          <t>707; 5989</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3354</t>
+          <t>0; 3500</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>667; 6175</t>
+          <t>665; 5549</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>669; 6431</t>
+          <t>687; 6307</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>722; 7347</t>
+          <t>0; 7389</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>830; 7761</t>
+          <t>1437; 8168</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2192; 10455</t>
+          <t>2143; 9977</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>712; 7787</t>
+          <t>709; 8323</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3249</t>
+          <t>0; 3847</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>533; 4908</t>
+          <t>535; 5359</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>673; 6588</t>
+          <t>680; 6149</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4300</t>
+          <t>0; 4214</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>0; 3301</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>681; 6171</t>
+          <t>685; 6608</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1839; 8599</t>
+          <t>1953; 8697</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5140</t>
+          <t>0; 4429</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>763; 7147</t>
+          <t>766; 6688</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1945; 9009</t>
+          <t>1900; 8518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3935; 12151</t>
+          <t>3931; 12582</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>667; 6214</t>
+          <t>645; 5959</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>796; 7608</t>
+          <t>842; 8332</t>
         </is>
       </c>
     </row>
@@ -2061,37 +2061,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3482</t>
+          <t>0; 3452</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4733</t>
+          <t>0; 4555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1045; 6627</t>
+          <t>1152; 7116</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2668</t>
+          <t>0; 3277</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3335</t>
+          <t>0; 3611</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3568</t>
+          <t>0; 4161</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3516</t>
+          <t>0; 4652</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2101,22 +2101,22 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 4526</t>
+          <t>0; 4496</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>644; 6031</t>
+          <t>643; 5780</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1597; 8352</t>
+          <t>1286; 7928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 2622</t>
+          <t>0; 2113</t>
         </is>
       </c>
     </row>
@@ -2269,22 +2269,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>680; 5862</t>
+          <t>677; 6598</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>787; 7397</t>
+          <t>798; 7592</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3732</t>
+          <t>0; 3772</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4518</t>
+          <t>0; 4092</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2294,37 +2294,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>679; 6793</t>
+          <t>678; 6858</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3367</t>
+          <t>0; 3334</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 6228</t>
+          <t>0; 4676</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>682; 6415</t>
+          <t>680; 6620</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2771; 10632</t>
+          <t>2830; 10775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 4926</t>
+          <t>0; 4622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>165; 5732</t>
+          <t>167; 5448</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2795; 11970</t>
+          <t>2791; 11054</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4907; 15396</t>
+          <t>5479; 16503</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2254; 9348</t>
+          <t>2156; 9219</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>684; 6553</t>
+          <t>743; 7180</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2687; 10342</t>
+          <t>2507; 11529</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6736; 17923</t>
+          <t>7120; 17336</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2453; 11722</t>
+          <t>2438; 11252</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1015; 8430</t>
+          <t>1033; 9551</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7173; 18806</t>
+          <t>6774; 17910</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13781; 28689</t>
+          <t>13409; 28347</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6434; 16695</t>
+          <t>5896; 16314</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2712; 11845</t>
+          <t>2673; 12489</t>
         </is>
       </c>
     </row>
